--- a/GDL-2019.xlsx
+++ b/GDL-2019.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87694068-C154-41E4-BD34-7BC3F320A9BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652E4164-F989-43D0-9B30-3243C6305BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GDL-2019.xlsx
+++ b/GDL-2019.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\i18n\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{652E4164-F989-43D0-9B30-3243C6305BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8877A5DC-FCCF-4024-8469-4FB6CEBEB757}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2613,7 +2613,7 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B60" s="1">
@@ -2671,7 +2671,7 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B62" s="1">
@@ -2874,7 +2874,7 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B69" s="1">
@@ -2903,7 +2903,7 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>77</v>
       </c>
       <c r="B70" s="1">
@@ -3019,7 +3019,7 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>81</v>
       </c>
       <c r="B74" s="1">
@@ -3048,7 +3048,7 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>82</v>
       </c>
       <c r="B75" s="1">
@@ -3077,7 +3077,7 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B76" s="1">
@@ -3106,7 +3106,7 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>84</v>
       </c>
       <c r="B77" s="1">
@@ -3135,7 +3135,7 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>85</v>
       </c>
       <c r="B78" s="1">

--- a/GDL-2019.xlsx
+++ b/GDL-2019.xlsx
@@ -1654,7 +1654,7 @@
       </c>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="4" t="s">
         <v>38</v>
       </c>
       <c r="B31" s="1" t="n">
